--- a/SHGraduationWarning/Template/學期成績匯入檔樣板.xlsx
+++ b/SHGraduationWarning/Template/學期成績匯入檔樣板.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ischoolProject\ScoreReportDAL\SHGraduationWarning\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD832B20-3E9C-4647-AB42-4D229994E890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2288EF02-52E5-4DC4-AFDB-EA2BB3335166}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A9D29B33-8A43-4C48-AF15-A43D4227393C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>學生系統編號</t>
   </si>
@@ -91,6 +91,10 @@
   </si>
   <si>
     <t>報部科目名稱</t>
+  </si>
+  <si>
+    <t>學分數</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -161,9 +165,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 佈景主題">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主題">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -201,7 +205,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -307,7 +311,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -449,7 +453,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -457,14 +461,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62F6E5AF-6710-43FC-828D-085D6E2FA9CF}">
-  <dimension ref="A1:R1"/>
+  <dimension ref="A1:S1"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -511,12 +515,15 @@
         <v>16</v>
       </c>
       <c r="P1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>17</v>
       </c>
     </row>
